--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run5/epoch_20/per_file_predictions_epoch_20.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run5/epoch_20/per_file_predictions_epoch_20.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="468">
   <si>
     <t>Filename</t>
   </si>
@@ -808,607 +808,616 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9804,0.0031,0.0047,0.0002</t>
-  </si>
-  <si>
-    <t>0.0398,0.0010,0.0158,0.9699</t>
-  </si>
-  <si>
-    <t>0.9873,0.0015,0.0026,0.0008</t>
-  </si>
-  <si>
-    <t>0.0316,0.0041,0.0019,0.9830</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>0.9598,0.0063,0.0107,0.0005</t>
+  </si>
+  <si>
+    <t>0.0279,0.0003,0.0014,0.9879</t>
+  </si>
+  <si>
+    <t>0.9791,0.0017,0.0047,0.0017</t>
+  </si>
+  <si>
+    <t>0.0923,0.0019,0.0052,0.9497</t>
   </si>
   <si>
     <t>1.0000,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.7983,0.0289,0.1452,0.0010</t>
-  </si>
-  <si>
-    <t>0.4032,0.0113,0.6235,0.0009</t>
-  </si>
-  <si>
-    <t>0.1570,0.0215,0.8743,0.0004</t>
-  </si>
-  <si>
-    <t>0.0379,0.0074,0.9657,0.0005</t>
-  </si>
-  <si>
-    <t>0.7403,0.0137,0.2459,0.0031</t>
-  </si>
-  <si>
-    <t>0.0004,0.9989,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.0145,0.9840,0.0032,0.0000</t>
-  </si>
-  <si>
-    <t>0.2001,0.8276,0.0108,0.0004</t>
-  </si>
-  <si>
-    <t>0.0218,0.9772,0.0028,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9995,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.6260,0.0044,0.4246,0.0019</t>
-  </si>
-  <si>
-    <t>0.4817,0.0147,0.5100,0.0020</t>
-  </si>
-  <si>
-    <t>0.0137,0.0014,0.9897,0.0002</t>
-  </si>
-  <si>
-    <t>0.1793,0.0020,0.8587,0.0025</t>
-  </si>
-  <si>
-    <t>0.4123,0.0019,0.7114,0.0002</t>
-  </si>
-  <si>
-    <t>0.0187,0.0071,0.9834,0.0005</t>
-  </si>
-  <si>
-    <t>0.0142,0.0010,0.9858,0.0061</t>
-  </si>
-  <si>
-    <t>0.3716,0.3788,0.1194,0.0004</t>
-  </si>
-  <si>
-    <t>0.7023,0.1105,0.1421,0.0013</t>
-  </si>
-  <si>
-    <t>0.0026,0.0248,0.9948,0.0002</t>
-  </si>
-  <si>
-    <t>0.1643,0.4713,0.1637,0.0002</t>
-  </si>
-  <si>
-    <t>0.9392,0.0283,0.0103,0.0011</t>
-  </si>
-  <si>
-    <t>0.9384,0.0251,0.0228,0.0009</t>
-  </si>
-  <si>
-    <t>0.9896,0.0075,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.0962,0.8505,0.0648,0.0013</t>
-  </si>
-  <si>
-    <t>0.0039,0.8558,0.6669,0.0002</t>
-  </si>
-  <si>
-    <t>0.0223,0.0251,0.9534,0.0056</t>
-  </si>
-  <si>
-    <t>0.0071,0.6470,0.8924,0.0007</t>
-  </si>
-  <si>
-    <t>0.0254,0.0056,0.9750,0.0015</t>
-  </si>
-  <si>
-    <t>0.0048,0.6119,0.8949,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9960,0.0342,0.0000</t>
-  </si>
-  <si>
-    <t>0.0052,0.1646,0.9795,0.0001</t>
-  </si>
-  <si>
-    <t>0.1082,0.1687,0.0130,0.8578</t>
-  </si>
-  <si>
-    <t>0.0003,0.9988,0.0012,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.9982,0.0005,0.0000</t>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.8159,0.0078,0.1842,0.0012</t>
+  </si>
+  <si>
+    <t>0.2466,0.0180,0.7574,0.0014</t>
+  </si>
+  <si>
+    <t>0.2858,0.0079,0.7792,0.0006</t>
+  </si>
+  <si>
+    <t>0.1418,0.0328,0.8259,0.0011</t>
+  </si>
+  <si>
+    <t>0.8052,0.0497,0.0668,0.0114</t>
+  </si>
+  <si>
+    <t>0.0011,0.9976,0.0013,0.0000</t>
+  </si>
+  <si>
+    <t>0.0040,0.9938,0.0026,0.0000</t>
+  </si>
+  <si>
+    <t>0.3187,0.7344,0.0089,0.0007</t>
+  </si>
+  <si>
+    <t>0.0190,0.9810,0.0018,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.9985,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.8387,0.0053,0.1406,0.0031</t>
+  </si>
+  <si>
+    <t>0.4951,0.0050,0.5577,0.0012</t>
+  </si>
+  <si>
+    <t>0.1031,0.0029,0.9157,0.0021</t>
+  </si>
+  <si>
+    <t>0.1216,0.0124,0.8906,0.0006</t>
+  </si>
+  <si>
+    <t>0.1201,0.0030,0.9175,0.0005</t>
+  </si>
+  <si>
+    <t>0.0436,0.0048,0.9686,0.0006</t>
+  </si>
+  <si>
+    <t>0.0135,0.0013,0.9896,0.0007</t>
+  </si>
+  <si>
+    <t>0.6609,0.2515,0.0629,0.0007</t>
+  </si>
+  <si>
+    <t>0.8117,0.0508,0.0961,0.0010</t>
+  </si>
+  <si>
+    <t>0.0039,0.0300,0.9924,0.0003</t>
+  </si>
+  <si>
+    <t>0.1032,0.7738,0.0567,0.0001</t>
+  </si>
+  <si>
+    <t>0.9847,0.0028,0.0030,0.0011</t>
+  </si>
+  <si>
+    <t>0.9481,0.0089,0.0216,0.0008</t>
+  </si>
+  <si>
+    <t>0.9551,0.0399,0.0046,0.0003</t>
+  </si>
+  <si>
+    <t>0.0306,0.9110,0.1134,0.0005</t>
+  </si>
+  <si>
+    <t>0.0027,0.8879,0.5971,0.0003</t>
+  </si>
+  <si>
+    <t>0.0299,0.0183,0.9446,0.0105</t>
+  </si>
+  <si>
+    <t>0.0469,0.1146,0.8934,0.0006</t>
+  </si>
+  <si>
+    <t>0.0235,0.0003,0.9843,0.0010</t>
+  </si>
+  <si>
+    <t>0.0005,0.7748,0.9786,0.0000</t>
+  </si>
+  <si>
+    <t>0.0014,0.9933,0.0136,0.0000</t>
+  </si>
+  <si>
+    <t>0.0191,0.0843,0.9530,0.0007</t>
+  </si>
+  <si>
+    <t>0.3273,0.0889,0.0596,0.5053</t>
+  </si>
+  <si>
+    <t>0.0001,0.9993,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.9975,0.0021,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.9999,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.0012,0.0193,0.9965,0.0002</t>
-  </si>
-  <si>
-    <t>0.0053,0.0136,0.9921,0.0002</t>
-  </si>
-  <si>
-    <t>0.0353,0.0037,0.9643,0.0032</t>
-  </si>
-  <si>
-    <t>0.0300,0.0004,0.9834,0.0004</t>
-  </si>
-  <si>
-    <t>0.0180,0.0078,0.9830,0.0002</t>
-  </si>
-  <si>
-    <t>0.0213,0.0068,0.9822,0.0002</t>
-  </si>
-  <si>
-    <t>0.9990,0.0004,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.0021,0.9985,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9971,0.7416,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.0191,0.9981,0.0000</t>
-  </si>
-  <si>
-    <t>0.0063,0.0621,0.9844,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9785,0.9728,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0005,0.9996,0.0002</t>
-  </si>
-  <si>
-    <t>0.0017,0.9971,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.9994,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9840,0.0006,0.0083,0.0003</t>
-  </si>
-  <si>
-    <t>0.5003,0.0118,0.5412,0.0011</t>
-  </si>
-  <si>
-    <t>0.0021,0.0062,0.9974,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9715,0.9517,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9872,0.8394,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.9903,0.0844,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9943,0.8078,0.0000</t>
-  </si>
-  <si>
-    <t>0.1117,0.0037,0.0190,0.9054</t>
-  </si>
-  <si>
-    <t>0.0028,0.0002,0.0001,0.9988</t>
-  </si>
-  <si>
-    <t>0.0099,0.0002,0.0001,0.9970</t>
-  </si>
-  <si>
-    <t>0.0166,0.0008,0.0158,0.9856</t>
-  </si>
-  <si>
-    <t>0.0375,0.0004,0.0032,0.9806</t>
-  </si>
-  <si>
-    <t>0.0046,0.0034,0.0048,0.9948</t>
-  </si>
-  <si>
-    <t>0.0084,0.9446,0.1097,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.9559,0.9339,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9039,0.9769,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9456,0.9676,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.9787,0.4634,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9829,0.8036,0.0000</t>
-  </si>
-  <si>
-    <t>0.0020,0.0012,0.9985,0.0000</t>
-  </si>
-  <si>
-    <t>0.1005,0.0380,0.8797,0.0004</t>
-  </si>
-  <si>
-    <t>0.7598,0.0071,0.2347,0.0024</t>
-  </si>
-  <si>
-    <t>0.1207,0.0127,0.8929,0.0004</t>
-  </si>
-  <si>
-    <t>0.0055,0.9947,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0135,0.9903,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.1130,0.9213,0.0017,0.0001</t>
-  </si>
-  <si>
-    <t>0.0429,0.9626,0.0021,0.0001</t>
-  </si>
-  <si>
-    <t>0.0040,0.9951,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.0022,0.9977,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.6247,0.5179,0.0040,0.0001</t>
-  </si>
-  <si>
-    <t>0.8836,0.0061,0.0895,0.0019</t>
-  </si>
-  <si>
-    <t>0.3073,0.0036,0.7524,0.0007</t>
-  </si>
-  <si>
-    <t>0.4697,0.0033,0.5835,0.0028</t>
-  </si>
-  <si>
-    <t>0.6202,0.0067,0.4177,0.0023</t>
-  </si>
-  <si>
-    <t>0.0934,0.0487,0.6508,0.1437</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0018,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.9976,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9984,0.9251,0.0000</t>
-  </si>
-  <si>
-    <t>0.1777,0.8682,0.0051,0.0000</t>
-  </si>
-  <si>
-    <t>0.9398,0.0465,0.0057,0.0007</t>
-  </si>
-  <si>
-    <t>0.9625,0.0302,0.0041,0.0002</t>
-  </si>
-  <si>
-    <t>0.9977,0.0010,0.0003,0.0001</t>
+    <t>0.0014,0.0304,0.9961,0.0001</t>
+  </si>
+  <si>
+    <t>0.0120,0.0051,0.9875,0.0004</t>
+  </si>
+  <si>
+    <t>0.2009,0.0015,0.8675,0.0005</t>
+  </si>
+  <si>
+    <t>0.0804,0.0013,0.9481,0.0011</t>
+  </si>
+  <si>
+    <t>0.0651,0.0752,0.8720,0.0004</t>
+  </si>
+  <si>
+    <t>0.0460,0.0026,0.9642,0.0005</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0011,0.0024,0.9988,0.0001</t>
   </si>
   <si>
     <t>0.9998,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9995,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0005,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0245,0.1768,0.8812,0.0019</t>
-  </si>
-  <si>
-    <t>0.0004,0.6536,0.9854,0.0000</t>
-  </si>
-  <si>
-    <t>0.0114,0.1507,0.9416,0.0008</t>
-  </si>
-  <si>
-    <t>0.0062,0.4695,0.9336,0.0002</t>
-  </si>
-  <si>
-    <t>0.9311,0.0055,0.0362,0.0009</t>
-  </si>
-  <si>
-    <t>0.6806,0.0554,0.2255,0.0012</t>
-  </si>
-  <si>
-    <t>0.4152,0.0014,0.7039,0.0011</t>
-  </si>
-  <si>
-    <t>0.9261,0.0031,0.0461,0.0010</t>
-  </si>
-  <si>
-    <t>0.1346,0.0011,0.0021,0.9382</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.0004,0.0013,0.0003,0.9995</t>
-  </si>
-  <si>
-    <t>0.0016,0.0003,0.0018,0.9987</t>
-  </si>
-  <si>
-    <t>0.0001,0.9867,0.8853,0.0000</t>
-  </si>
-  <si>
-    <t>0.8521,0.2677,0.0017,0.0000</t>
-  </si>
-  <si>
-    <t>0.9923,0.0049,0.0008,0.0001</t>
+    <t>0.9993,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9980,0.7492,0.0000</t>
+  </si>
+  <si>
+    <t>0.0014,0.0341,0.9958,0.0001</t>
+  </si>
+  <si>
+    <t>0.0186,0.0119,0.9771,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.9843,0.8747,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0037,0.9989,0.0002</t>
+  </si>
+  <si>
+    <t>0.0075,0.9921,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.9995,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.5054,0.0042,0.5958,0.0007</t>
+  </si>
+  <si>
+    <t>0.8546,0.0355,0.0699,0.0010</t>
+  </si>
+  <si>
+    <t>0.0005,0.0348,0.9984,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9526,0.9478,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9859,0.6993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9994,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9939,0.5824,0.0000</t>
+  </si>
+  <si>
+    <t>0.1086,0.0011,0.0595,0.8692</t>
+  </si>
+  <si>
+    <t>0.0003,0.0004,0.0002,0.9997</t>
+  </si>
+  <si>
+    <t>0.0051,0.0002,0.0000,0.9984</t>
+  </si>
+  <si>
+    <t>0.0048,0.0008,0.0066,0.9953</t>
+  </si>
+  <si>
+    <t>0.1430,0.0015,0.0409,0.8668</t>
+  </si>
+  <si>
+    <t>0.0031,0.0030,0.0004,0.9977</t>
+  </si>
+  <si>
+    <t>0.0016,0.9855,0.0602,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9521,0.9462,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.8426,0.9905,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.8726,0.9088,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.9848,0.5949,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9753,0.7865,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0006,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0681,0.0390,0.9120,0.0007</t>
+  </si>
+  <si>
+    <t>0.8284,0.0168,0.1304,0.0014</t>
+  </si>
+  <si>
+    <t>0.0541,0.0124,0.9538,0.0002</t>
+  </si>
+  <si>
+    <t>0.0147,0.9872,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0092,0.9925,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.2214,0.8362,0.0050,0.0001</t>
+  </si>
+  <si>
+    <t>0.1307,0.9018,0.0029,0.0002</t>
+  </si>
+  <si>
+    <t>0.0139,0.9874,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0050,0.9955,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.8748,0.2172,0.0021,0.0001</t>
+  </si>
+  <si>
+    <t>0.5896,0.0060,0.4615,0.0012</t>
+  </si>
+  <si>
+    <t>0.3560,0.0042,0.7253,0.0009</t>
+  </si>
+  <si>
+    <t>0.2610,0.1610,0.5144,0.0030</t>
+  </si>
+  <si>
+    <t>0.3453,0.0208,0.6265,0.0045</t>
+  </si>
+  <si>
+    <t>0.3054,0.0086,0.3712,0.2204</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.0017,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9995,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.9958,0.0017,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9990,0.9432,0.0000</t>
+  </si>
+  <si>
+    <t>0.0472,0.9610,0.0028,0.0000</t>
+  </si>
+  <si>
+    <t>0.8796,0.1318,0.0110,0.0003</t>
+  </si>
+  <si>
+    <t>0.8022,0.2569,0.0065,0.0004</t>
+  </si>
+  <si>
+    <t>0.9974,0.0014,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0027,0.9639,0.2175,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.9142,0.9654,0.0000</t>
+  </si>
+  <si>
+    <t>0.0015,0.0966,0.9943,0.0000</t>
+  </si>
+  <si>
+    <t>0.0044,0.0844,0.9873,0.0001</t>
+  </si>
+  <si>
+    <t>0.9403,0.0062,0.0248,0.0004</t>
+  </si>
+  <si>
+    <t>0.3931,0.0184,0.6131,0.0018</t>
+  </si>
+  <si>
+    <t>0.6579,0.0009,0.4511,0.0007</t>
+  </si>
+  <si>
+    <t>0.8820,0.0380,0.0338,0.0009</t>
+  </si>
+  <si>
+    <t>0.3413,0.0008,0.0024,0.8284</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.0003,0.9998</t>
+  </si>
+  <si>
+    <t>0.0002,0.0048,0.0001,0.9997</t>
+  </si>
+  <si>
+    <t>0.0005,0.0001,0.0008,0.9996</t>
+  </si>
+  <si>
+    <t>0.0001,0.9839,0.8976,0.0000</t>
+  </si>
+  <si>
+    <t>0.3125,0.8379,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.8618,0.2145,0.0036,0.0001</t>
   </si>
   <si>
     <t>0.9995,0.0000,0.0000,0.0001</t>
   </si>
   <si>
-    <t>0.7438,0.0006,0.0066,0.3480</t>
-  </si>
-  <si>
-    <t>0.0011,0.0991,0.9947,0.0001</t>
-  </si>
-  <si>
-    <t>0.9941,0.0001,0.0011,0.0017</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.1885,0.7305,0.0581,0.0004</t>
-  </si>
-  <si>
-    <t>0.9801,0.0035,0.0048,0.0009</t>
-  </si>
-  <si>
-    <t>0.9694,0.0027,0.0162,0.0004</t>
-  </si>
-  <si>
-    <t>0.1535,0.8271,0.0229,0.0004</t>
-  </si>
-  <si>
-    <t>0.9270,0.0050,0.0528,0.0006</t>
-  </si>
-  <si>
-    <t>0.9638,0.0198,0.0058,0.0003</t>
+    <t>0.5522,0.0008,0.0049,0.6189</t>
+  </si>
+  <si>
+    <t>0.0011,0.0587,0.9959,0.0002</t>
+  </si>
+  <si>
+    <t>0.9912,0.0002,0.0020,0.0036</t>
+  </si>
+  <si>
+    <t>0.9987,0.0001,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.3445,0.5883,0.0624,0.0008</t>
+  </si>
+  <si>
+    <t>0.9683,0.0102,0.0043,0.0012</t>
+  </si>
+  <si>
+    <t>0.9905,0.0012,0.0032,0.0003</t>
+  </si>
+  <si>
+    <t>0.1094,0.8825,0.0158,0.0002</t>
+  </si>
+  <si>
+    <t>0.8145,0.0059,0.1985,0.0003</t>
+  </si>
+  <si>
+    <t>0.9463,0.0410,0.0074,0.0002</t>
   </si>
   <si>
     <t>0.9997,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.5696,0.5270,0.0064,0.0004</t>
-  </si>
-  <si>
-    <t>0.9898,0.0056,0.0011,0.0002</t>
-  </si>
-  <si>
-    <t>0.8162,0.3262,0.0019,0.0000</t>
-  </si>
-  <si>
-    <t>0.9096,0.0116,0.0634,0.0011</t>
-  </si>
-  <si>
-    <t>0.9933,0.0048,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9906,0.0037,0.0011,0.0006</t>
-  </si>
-  <si>
-    <t>0.9987,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9814,0.0149,0.0019,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.0069,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.9975,0.0006,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0010,0.0014,0.9989,0.0001</t>
-  </si>
-  <si>
-    <t>0.0040,0.1527,0.9810,0.0004</t>
-  </si>
-  <si>
-    <t>0.0026,0.0039,0.9973,0.0002</t>
-  </si>
-  <si>
-    <t>0.0056,0.1632,0.9735,0.0004</t>
-  </si>
-  <si>
-    <t>0.0055,0.0236,0.9898,0.0003</t>
-  </si>
-  <si>
-    <t>0.0006,0.0005,0.9994,0.0001</t>
-  </si>
-  <si>
-    <t>0.0032,0.0031,0.9966,0.0002</t>
-  </si>
-  <si>
-    <t>0.0519,0.0404,0.9300,0.0007</t>
-  </si>
-  <si>
-    <t>0.3771,0.0053,0.6861,0.0010</t>
-  </si>
-  <si>
-    <t>0.3375,0.0084,0.7068,0.0026</t>
-  </si>
-  <si>
-    <t>0.4347,0.4135,0.0702,0.0003</t>
-  </si>
-  <si>
-    <t>0.1066,0.5484,0.2460,0.0002</t>
-  </si>
-  <si>
-    <t>0.8717,0.0385,0.0508,0.0004</t>
-  </si>
-  <si>
-    <t>0.5671,0.0222,0.4018,0.0080</t>
-  </si>
-  <si>
-    <t>0.0949,0.0617,0.8774,0.0006</t>
-  </si>
-  <si>
-    <t>0.9322,0.0958,0.0031,0.0001</t>
-  </si>
-  <si>
-    <t>0.9823,0.0253,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.9875,0.0112,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.8917,0.0427,0.0242,0.0003</t>
-  </si>
-  <si>
-    <t>0.8562,0.0094,0.1175,0.0014</t>
-  </si>
-  <si>
-    <t>0.8369,0.0124,0.0922,0.0097</t>
-  </si>
-  <si>
-    <t>0.8515,0.0039,0.1418,0.0017</t>
-  </si>
-  <si>
-    <t>0.8589,0.0027,0.1568,0.0007</t>
-  </si>
-  <si>
-    <t>0.0089,0.0012,0.9942,0.0001</t>
-  </si>
-  <si>
-    <t>0.0073,0.2276,0.9612,0.0006</t>
-  </si>
-  <si>
-    <t>0.0087,0.1387,0.9651,0.0006</t>
-  </si>
-  <si>
-    <t>0.0009,0.3818,0.9872,0.0001</t>
-  </si>
-  <si>
-    <t>0.0141,0.0323,0.9689,0.0013</t>
-  </si>
-  <si>
-    <t>0.0669,0.0138,0.9409,0.0007</t>
-  </si>
-  <si>
-    <t>0.3001,0.7196,0.0155,0.0009</t>
-  </si>
-  <si>
-    <t>0.9597,0.0013,0.0307,0.0012</t>
-  </si>
-  <si>
-    <t>0.0083,0.0142,0.9900,0.0000</t>
-  </si>
-  <si>
-    <t>0.0062,0.0120,0.9902,0.0003</t>
-  </si>
-  <si>
-    <t>0.0033,0.4883,0.9591,0.0002</t>
-  </si>
-  <si>
-    <t>0.0017,0.0034,0.9984,0.0000</t>
-  </si>
-  <si>
-    <t>0.0271,0.0043,0.9753,0.0005</t>
-  </si>
-  <si>
-    <t>0.0010,0.0064,0.9990,0.0000</t>
-  </si>
-  <si>
-    <t>0.0075,0.0085,0.9896,0.0003</t>
-  </si>
-  <si>
-    <t>0.0119,0.0080,0.9870,0.0003</t>
-  </si>
-  <si>
-    <t>0.8119,0.0040,0.2078,0.0007</t>
-  </si>
-  <si>
-    <t>0.7708,0.0071,0.2183,0.0040</t>
-  </si>
-  <si>
-    <t>0.7608,0.0031,0.2770,0.0025</t>
+    <t>0.8730,0.1339,0.0078,0.0009</t>
+  </si>
+  <si>
+    <t>0.9949,0.0029,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9478,0.0737,0.0021,0.0001</t>
+  </si>
+  <si>
+    <t>0.9847,0.0092,0.0020,0.0004</t>
+  </si>
+  <si>
+    <t>0.9936,0.0049,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9960,0.0008,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9690,0.0367,0.0020,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0026,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.9959,0.0008,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.0021,0.0014,0.9981,0.0001</t>
+  </si>
+  <si>
+    <t>0.0059,0.1256,0.9778,0.0004</t>
+  </si>
+  <si>
+    <t>0.0221,0.0011,0.9881,0.0002</t>
+  </si>
+  <si>
+    <t>0.0223,0.3104,0.8204,0.0007</t>
+  </si>
+  <si>
+    <t>0.0066,0.0156,0.9910,0.0002</t>
+  </si>
+  <si>
+    <t>0.0101,0.0009,0.9931,0.0003</t>
+  </si>
+  <si>
+    <t>0.0113,0.0084,0.9884,0.0002</t>
+  </si>
+  <si>
+    <t>0.1530,0.0502,0.7921,0.0038</t>
+  </si>
+  <si>
+    <t>0.4324,0.0048,0.6718,0.0004</t>
+  </si>
+  <si>
+    <t>0.5905,0.1303,0.2142,0.0012</t>
+  </si>
+  <si>
+    <t>0.2127,0.4832,0.1700,0.0003</t>
+  </si>
+  <si>
+    <t>0.5205,0.0545,0.3837,0.0016</t>
+  </si>
+  <si>
+    <t>0.8134,0.0164,0.1396,0.0004</t>
+  </si>
+  <si>
+    <t>0.6038,0.0120,0.4157,0.0036</t>
+  </si>
+  <si>
+    <t>0.4380,0.0757,0.4747,0.0025</t>
+  </si>
+  <si>
+    <t>0.9924,0.0045,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.9423,0.0821,0.0026,0.0001</t>
+  </si>
+  <si>
+    <t>0.9943,0.0033,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9983,0.0010,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9970,0.0026,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.8805,0.0351,0.0407,0.0006</t>
+  </si>
+  <si>
+    <t>0.9378,0.0123,0.0196,0.0002</t>
+  </si>
+  <si>
+    <t>0.9002,0.0086,0.0535,0.0021</t>
+  </si>
+  <si>
+    <t>0.7893,0.0034,0.2457,0.0010</t>
+  </si>
+  <si>
+    <t>0.9130,0.0050,0.0632,0.0007</t>
+  </si>
+  <si>
+    <t>0.0026,0.0009,0.9976,0.0002</t>
+  </si>
+  <si>
+    <t>0.0010,0.2263,0.9920,0.0002</t>
+  </si>
+  <si>
+    <t>0.0225,0.5648,0.7188,0.0005</t>
+  </si>
+  <si>
+    <t>0.0013,0.1949,0.9923,0.0000</t>
+  </si>
+  <si>
+    <t>0.0135,0.0267,0.9714,0.0014</t>
   </si>
   <si>
     <t>0.9998,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0163,0.4679,0.8076,0.0005</t>
-  </si>
-  <si>
-    <t>0.0078,0.0027,0.9921,0.0002</t>
-  </si>
-  <si>
-    <t>0.0045,0.4907,0.9193,0.0002</t>
-  </si>
-  <si>
-    <t>0.0198,0.0308,0.9680,0.0004</t>
-  </si>
-  <si>
-    <t>0.1260,0.0004,0.9385,0.0002</t>
-  </si>
-  <si>
-    <t>0.0701,0.0021,0.9485,0.0018</t>
-  </si>
-  <si>
-    <t>0.0522,0.0062,0.9601,0.0004</t>
-  </si>
-  <si>
-    <t>0.0768,0.0003,0.9567,0.0006</t>
-  </si>
-  <si>
-    <t>0.9907,0.0002,0.0013,0.0052</t>
-  </si>
-  <si>
-    <t>0.0192,0.0116,0.0018,0.9847</t>
-  </si>
-  <si>
-    <t>0.1572,0.0004,0.0032,0.9301</t>
-  </si>
-  <si>
-    <t>0.0015,0.0001,0.0011,0.9990</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.9361,0.0021,0.0182,0.0148</t>
+    <t>0.0223,0.0091,0.9795,0.0006</t>
+  </si>
+  <si>
+    <t>0.6981,0.2373,0.0402,0.0007</t>
+  </si>
+  <si>
+    <t>0.9368,0.0052,0.0369,0.0025</t>
+  </si>
+  <si>
+    <t>0.0237,0.0016,0.9829,0.0002</t>
+  </si>
+  <si>
+    <t>0.0021,0.0230,0.9957,0.0001</t>
+  </si>
+  <si>
+    <t>0.0093,0.4989,0.8737,0.0002</t>
+  </si>
+  <si>
+    <t>0.0005,0.0035,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0485,0.0031,0.9621,0.0004</t>
+  </si>
+  <si>
+    <t>0.0040,0.0082,0.9960,0.0000</t>
+  </si>
+  <si>
+    <t>0.0370,0.0061,0.9634,0.0006</t>
+  </si>
+  <si>
+    <t>0.0561,0.0120,0.9498,0.0006</t>
+  </si>
+  <si>
+    <t>0.6642,0.0015,0.3997,0.0032</t>
+  </si>
+  <si>
+    <t>0.7619,0.0091,0.2365,0.0021</t>
+  </si>
+  <si>
+    <t>0.9112,0.0056,0.0617,0.0016</t>
+  </si>
+  <si>
+    <t>0.0110,0.3471,0.9008,0.0004</t>
+  </si>
+  <si>
+    <t>0.0020,0.0094,0.9965,0.0001</t>
+  </si>
+  <si>
+    <t>0.0206,0.4813,0.6973,0.0003</t>
+  </si>
+  <si>
+    <t>0.2336,0.0158,0.7667,0.0007</t>
+  </si>
+  <si>
+    <t>0.0500,0.0013,0.9696,0.0002</t>
+  </si>
+  <si>
+    <t>0.0329,0.0047,0.9677,0.0025</t>
+  </si>
+  <si>
+    <t>0.1329,0.0067,0.8836,0.0020</t>
+  </si>
+  <si>
+    <t>0.0329,0.0014,0.9744,0.0010</t>
+  </si>
+  <si>
+    <t>0.9496,0.0003,0.0078,0.0430</t>
+  </si>
+  <si>
+    <t>0.0086,0.0106,0.0016,0.9918</t>
+  </si>
+  <si>
+    <t>0.1246,0.0010,0.0055,0.9308</t>
+  </si>
+  <si>
+    <t>0.0041,0.0001,0.0015,0.9977</t>
+  </si>
+  <si>
+    <t>0.0024,0.0029,0.0008,0.9979</t>
+  </si>
+  <si>
+    <t>0.7746,0.0107,0.0600,0.1161</t>
   </si>
 </sst>
 </file>
@@ -1794,7 +1803,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1808,7 +1817,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1822,7 +1831,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1836,7 +1845,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1850,7 +1859,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1864,7 +1873,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1878,7 +1887,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1892,7 +1901,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1906,7 +1915,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1920,7 +1929,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1934,7 +1943,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1948,7 +1957,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1962,7 +1971,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1976,7 +1985,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1990,7 +1999,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2004,7 +2013,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2018,7 +2027,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2032,7 +2041,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2046,7 +2055,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2060,7 +2069,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2074,7 +2083,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2088,7 +2097,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2102,7 +2111,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2116,7 +2125,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2130,7 +2139,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2144,7 +2153,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2158,7 +2167,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2172,7 +2181,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2186,7 +2195,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2200,7 +2209,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2214,7 +2223,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2228,7 +2237,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2239,10 +2248,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2256,7 +2265,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2270,7 +2279,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2284,7 +2293,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2298,7 +2307,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2312,7 +2321,7 @@
         <v>263</v>
       </c>
       <c r="D39" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2326,7 +2335,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2337,10 +2346,10 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2354,7 +2363,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2368,7 +2377,7 @@
         <v>263</v>
       </c>
       <c r="D43" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2382,7 +2391,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2396,7 +2405,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2410,7 +2419,7 @@
         <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2424,7 +2433,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2438,7 +2447,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2452,7 +2461,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2466,7 +2475,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2480,7 +2489,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2494,7 +2503,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2508,7 +2517,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2522,7 +2531,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2536,7 +2545,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2550,7 +2559,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2564,7 +2573,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2578,7 +2587,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>313</v>
+        <v>271</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2592,7 +2601,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2606,7 +2615,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2620,7 +2629,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2634,7 +2643,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2648,7 +2657,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2662,7 +2671,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2676,7 +2685,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2690,7 +2699,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2704,7 +2713,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2718,7 +2727,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2732,7 +2741,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2743,10 +2752,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D70" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2757,10 +2766,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2774,7 +2783,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2788,7 +2797,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2802,7 +2811,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2816,7 +2825,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2830,7 +2839,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2844,7 +2853,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2858,7 +2867,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2872,7 +2881,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2886,7 +2895,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2900,7 +2909,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2914,7 +2923,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2928,7 +2937,7 @@
         <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2942,7 +2951,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2956,7 +2965,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2970,7 +2979,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2981,10 +2990,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -2998,7 +3007,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3012,7 +3021,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3026,7 +3035,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>313</v>
+        <v>272</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3040,7 +3049,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>313</v>
+        <v>272</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3054,7 +3063,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>313</v>
+        <v>271</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3068,7 +3077,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>313</v>
+        <v>272</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3082,7 +3091,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3096,7 +3105,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>313</v>
+        <v>271</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3110,7 +3119,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3124,7 +3133,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3138,7 +3147,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3152,7 +3161,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3166,7 +3175,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3180,7 +3189,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3194,7 +3203,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3208,7 +3217,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3222,7 +3231,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3236,7 +3245,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3250,7 +3259,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3264,7 +3273,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3278,7 +3287,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3292,7 +3301,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3306,7 +3315,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3320,7 +3329,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3334,7 +3343,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3348,7 +3357,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3362,7 +3371,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3373,10 +3382,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3390,7 +3399,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3404,7 +3413,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3418,7 +3427,7 @@
         <v>261</v>
       </c>
       <c r="D118" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3429,10 +3438,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3443,10 +3452,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D120" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3460,7 +3469,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3474,7 +3483,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3488,7 +3497,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3502,7 +3511,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3516,7 +3525,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3530,7 +3539,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3544,7 +3553,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3558,7 +3567,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3572,7 +3581,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>366</v>
+        <v>272</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3586,7 +3595,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>313</v>
+        <v>272</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3600,7 +3609,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3614,7 +3623,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>366</v>
+        <v>272</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3628,7 +3637,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3642,7 +3651,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3656,7 +3665,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3667,10 +3676,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D136" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3684,7 +3693,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3698,7 +3707,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3712,7 +3721,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3726,7 +3735,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3737,10 +3746,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3751,10 +3760,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D142" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3768,7 +3777,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3782,7 +3791,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3796,7 +3805,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3810,7 +3819,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3824,7 +3833,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3838,7 +3847,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3852,7 +3861,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3863,10 +3872,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3880,7 +3889,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>366</v>
+        <v>318</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3894,7 +3903,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3908,7 +3917,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3919,10 +3928,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D154" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3936,7 +3945,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>313</v>
+        <v>272</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -3950,7 +3959,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -3964,7 +3973,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -3978,7 +3987,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -3992,7 +4001,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4006,7 +4015,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4020,7 +4029,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4034,7 +4043,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4048,7 +4057,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4062,7 +4071,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4076,7 +4085,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4090,7 +4099,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4104,7 +4113,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4118,7 +4127,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>313</v>
+        <v>271</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4132,7 +4141,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>366</v>
+        <v>272</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4146,7 +4155,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4160,7 +4169,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>313</v>
+        <v>272</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4174,7 +4183,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>313</v>
+        <v>272</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4185,10 +4194,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4202,7 +4211,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4216,7 +4225,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4230,7 +4239,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4244,7 +4253,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4258,7 +4267,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4272,7 +4281,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4286,7 +4295,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4300,7 +4309,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4314,7 +4323,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4328,7 +4337,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4342,7 +4351,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4356,7 +4365,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4370,7 +4379,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4384,7 +4393,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4398,7 +4407,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4412,7 +4421,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4426,7 +4435,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4440,7 +4449,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4451,10 +4460,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4465,10 +4474,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D193" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4479,10 +4488,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D194" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4496,7 +4505,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4510,7 +4519,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4521,10 +4530,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D197" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4538,7 +4547,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4552,7 +4561,7 @@
         <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4566,7 +4575,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4580,7 +4589,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4594,7 +4603,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4608,7 +4617,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4622,7 +4631,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4636,7 +4645,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4650,7 +4659,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4664,7 +4673,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4678,7 +4687,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4692,7 +4701,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4703,10 +4712,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D210" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4720,7 +4729,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4734,7 +4743,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4748,7 +4757,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4762,7 +4771,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>313</v>
+        <v>272</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4776,7 +4785,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>313</v>
+        <v>271</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4790,7 +4799,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>313</v>
+        <v>439</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4804,7 +4813,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>268</v>
+        <v>318</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4818,7 +4827,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>313</v>
+        <v>271</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4832,7 +4841,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4846,7 +4855,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4860,7 +4869,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4871,10 +4880,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D222" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4888,7 +4897,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4902,7 +4911,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4916,7 +4925,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4930,7 +4939,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -4944,7 +4953,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -4958,7 +4967,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -4972,7 +4981,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -4986,7 +4995,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5000,7 +5009,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5014,7 +5023,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5028,7 +5037,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5042,7 +5051,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5056,7 +5065,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>313</v>
+        <v>272</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5070,7 +5079,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5084,7 +5093,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>313</v>
+        <v>271</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5098,7 +5107,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>268</v>
+        <v>439</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5112,7 +5121,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>313</v>
+        <v>272</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5126,7 +5135,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>450</v>
+        <v>272</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5140,7 +5149,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>313</v>
+        <v>398</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5154,7 +5163,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>313</v>
+        <v>271</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5168,7 +5177,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5182,7 +5191,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5196,7 +5205,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5210,7 +5219,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5224,7 +5233,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5238,7 +5247,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5252,7 +5261,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5266,7 +5275,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5280,7 +5289,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5294,7 +5303,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5308,7 +5317,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5322,7 +5331,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5336,7 +5345,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5350,7 +5359,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
   </sheetData>
